--- a/besi/dist/20261025_BESI模型_v0.1.xlsx
+++ b/besi/dist/20261025_BESI模型_v0.1.xlsx
@@ -5255,7 +5255,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5487,7 +5487,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5574,7 +5574,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5658,7 +5658,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5742,7 +5742,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5826,7 +5826,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5910,7 +5910,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5997,7 +5997,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6111,7 +6111,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6195,7 +6195,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6279,7 +6279,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6363,7 +6363,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6447,7 +6447,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6723,7 +6723,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7045,7 +7045,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7166,7 +7166,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7287,7 +7287,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7408,7 +7408,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7529,7 +7529,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.1.xlsx</t>
     </r>
     <r>
       <rPr>
